--- a/Document/Buck/Buck.xlsx
+++ b/Document/Buck/Buck.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAC9A5C-0C42-4DEF-B86E-56D0FFA33D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE0C1CF-5C92-42E6-A371-9E9CC6AD5ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>Q1导通Q2关断给L1充电电感电流缓慢上升电感两端电压VL=VIN-VOUT</t>
   </si>
@@ -67,14 +67,25 @@
     <t>DCM</t>
   </si>
   <si>
-    <t>Q1关断Q2打开</t>
+    <t>BCM</t>
+  </si>
+  <si>
+    <t>Q1关断Q2电感L1释放(能量)电感电流慢慢减小(注意空载的情况同步整流一直开着)</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>同步 Buck（上下 MOS） 同步 Buck 默认会强制拉负电感电流（下管继续导通），
+如果不做零电流检测 ZCS，永远不会进入 DCM，只会进入CCM 负电流模式。这就是为什么我们调试逆变器的时候放电情况下，逆变器空载的时候电压还是稳定。 
+✅ 同步 Buck 想要 DCM：必须增加下管的 ZCS 检测，电感电流到 0 立刻关断下管，防止电流倒灌。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,13 +93,33 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="11">
@@ -209,50 +240,107 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -283,7 +371,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>305435</xdr:colOff>
+      <xdr:colOff>15543</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>46355</xdr:rowOff>
     </xdr:to>
@@ -981,9 +1069,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>183931</xdr:rowOff>
+      <xdr:colOff>8049</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -998,8 +1086,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8434552" y="6477000"/>
-          <a:ext cx="1202121" cy="374431"/>
+          <a:off x="8468784" y="6858000"/>
+          <a:ext cx="1219885" cy="381000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1124,8 +1212,8 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>7327</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>592965</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>6569</xdr:rowOff>
     </xdr:from>
@@ -1148,8 +1236,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="7850672" y="6483569"/>
-          <a:ext cx="597018" cy="374431"/>
+          <a:off x="11475613" y="6864569"/>
+          <a:ext cx="615632" cy="374431"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1181,9 +1269,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>183931</xdr:rowOff>
+      <xdr:colOff>5366</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>8049</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1198,8 +1286,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8434552" y="6477000"/>
-          <a:ext cx="1202121" cy="374431"/>
+          <a:off x="12074869" y="6858000"/>
+          <a:ext cx="1217201" cy="389049"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1500,6 +1588,1606 @@
         <a:xfrm>
           <a:off x="13264963" y="6479801"/>
           <a:ext cx="0" cy="182096"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>13939</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>594732</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{238E92CE-B18F-85C6-DCB0-7C83A9115DDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7856963" y="7824439"/>
+          <a:ext cx="594732" cy="359734"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9292</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>9293</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D27CC79F-1497-8D03-AFE7-A53F350C31A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9664390" y="7805854"/>
+          <a:ext cx="590086" cy="394939"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>590086</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>13939</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E6E6665-89CA-4BFD-A48D-F8E8807C614A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11453232" y="7810500"/>
+          <a:ext cx="590086" cy="394939"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>597713</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>179716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>11837</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>186905</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF664F0-544A-DE5F-B964-5254A97866B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8454676" y="8371216"/>
+          <a:ext cx="612881" cy="388189"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>3594</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36BFE167-E3C2-DF52-F204-751AC82F8B75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9076759" y="8758354"/>
+          <a:ext cx="595609" cy="8240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>593066</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>179716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7190</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>186905</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Straight Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B92C13E-82B7-47E9-824D-E3DF7E8F38B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8464670" y="8371216"/>
+          <a:ext cx="614633" cy="388189"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>3594</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C537C0E4-F27D-4D59-A6C2-59F5580E68D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9076759" y="8758354"/>
+          <a:ext cx="595609" cy="8240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>593066</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>179716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>7190</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>186905</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C13F8CE-CF87-4F93-8464-BA46035599BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8464670" y="8371216"/>
+          <a:ext cx="614633" cy="388189"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>3594</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B55ECC6-E1C8-4E4E-A31A-C9B7F6415698}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9076759" y="8758354"/>
+          <a:ext cx="595609" cy="8240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Straight Connector 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D91CD81-AB6D-4466-AF67-D8B7C291B266}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7861609" y="8953500"/>
+          <a:ext cx="594732" cy="373673"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>597713</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>179716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>11837</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>186905</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Straight Connector 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF5F230F-9C67-4CCE-B97B-0A739E1EA899}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8454676" y="8371216"/>
+          <a:ext cx="612881" cy="388189"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>3594</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76C7E546-5C7B-4F81-B16B-19A1FA21B875}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9060366" y="8758354"/>
+          <a:ext cx="594732" cy="8240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>596080</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>178210</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>596081</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>9218</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4BC8BCF-8814-402F-B221-9845859A1BE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9654048" y="8941210"/>
+          <a:ext cx="599154" cy="402508"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>597713</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>179716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>11837</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>186905</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="Straight Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F36536E1-45A3-4406-8FFD-C927773C02DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8454676" y="8942716"/>
+          <a:ext cx="612881" cy="388189"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>3594</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="Straight Connector 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38083B0B-7AEE-49D7-8CCC-B818FA6378E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9060366" y="9329854"/>
+          <a:ext cx="594732" cy="8240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>6145</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>172065</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>6145</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2798D476-C8C7-4478-92E8-9D8C6F7A752A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11460726" y="8935065"/>
+          <a:ext cx="593008" cy="405580"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>597713</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>179716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>11837</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>186905</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Straight Connector 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2ADCC21-6F86-4E12-895D-FEDA8D26045B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8454676" y="8942716"/>
+          <a:ext cx="612881" cy="388189"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>4646</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>185854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>3594</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="Straight Connector 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{729E67B9-7234-4786-82E6-FF276BD9E9FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9060366" y="9329854"/>
+          <a:ext cx="594732" cy="8240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>8283</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>10783</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>7189</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="Straight Connector 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C9D4D68-1C11-4DFA-C1D2-43C783FE358C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7879887" y="7239000"/>
+          <a:ext cx="2500" cy="197689"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>600254</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>2801</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>184898</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="Straight Connector 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B49BF16-3E10-4C16-AA5E-DBADDC7BA4EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="13273896" y="7239000"/>
+          <a:ext cx="2801" cy="184898"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>3073</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>521</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>8610</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="Straight Connector 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BF1F734-C5E9-4EEA-B8B9-3FE0F2EAEB4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7862734" y="9525521"/>
+          <a:ext cx="604691" cy="380479"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>184588</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="54" name="Straight Connector 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0111BF48-D806-4473-93B3-606AA0F69060}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8458815" y="10096500"/>
+          <a:ext cx="1205926" cy="375088"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>596660</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3595</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1941</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3074</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Straight Connector 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA13FA91-CAD2-4B27-945B-D54B95655A69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9668773" y="9528595"/>
+          <a:ext cx="605791" cy="380479"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>3594</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>10783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>11215</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>4871</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="Straight Connector 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5F04AB-B208-44CD-B818-05442615C6A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10276217" y="10107283"/>
+          <a:ext cx="1208130" cy="375088"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>596660</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3595</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1941</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3074</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="Straight Connector 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D1F08C8-0D2B-4DC3-8C93-B5C856CD63F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9668773" y="9528595"/>
+          <a:ext cx="605791" cy="380479"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>3594</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>10783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>11215</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>4871</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="Straight Connector 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E04488A-8692-4269-B371-DB053BAE717D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10276217" y="10107283"/>
+          <a:ext cx="1208130" cy="375088"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>5537</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>189979</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="Straight Connector 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C9C02A0-30D6-4384-946B-4DC789D20693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7856963" y="10668000"/>
+          <a:ext cx="604915" cy="380479"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>184588</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="Straight Connector 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B02A86E-0243-4FC1-A63D-DFE5E9AACB13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8456341" y="10668000"/>
+          <a:ext cx="1206377" cy="375088"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>5537</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>189979</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="Straight Connector 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCA52F81-8907-4C24-B266-6BC248F275A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7856963" y="10668000"/>
+          <a:ext cx="604915" cy="380479"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>184588</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="65" name="Straight Connector 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF14730-5281-4D65-BCF1-0D5C90C85D6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8456341" y="10668000"/>
+          <a:ext cx="1206377" cy="375088"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>5537</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>189979</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="Straight Connector 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B3716BD-D0B2-485A-AF1A-6BD3DD4C123B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9655098" y="10668000"/>
+          <a:ext cx="604915" cy="380479"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>599378</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>184588</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="69" name="Straight Connector 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2BE65C4-3AA2-4786-9091-3310B584F4CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10254476" y="10668000"/>
+          <a:ext cx="1206376" cy="375088"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1775,13 +3463,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A21:V49"/>
+  <dimension ref="A2:V68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="14:14">
+      <c r="N2" s="24"/>
+    </row>
     <row r="21" spans="1:22">
       <c r="A21">
         <v>1</v>
@@ -1792,9 +3484,21 @@
       <c r="H21" t="s">
         <v>1</v>
       </c>
-      <c r="K21" t="s">
+      <c r="J21" s="1"/>
+      <c r="K21" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="3"/>
     </row>
     <row r="22" spans="1:22">
       <c r="A22">
@@ -1803,271 +3507,805 @@
       <c r="B22" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="2"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="10"/>
-      <c r="S22" s="8"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="6"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="6"/>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="6"/>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="6"/>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="33"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="6"/>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" s="33"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="6"/>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" s="33"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="9"/>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" s="33"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="J29" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="3"/>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="A30" s="33"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="6"/>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="J31" s="26"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="6"/>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="J32" s="26"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="6"/>
+    </row>
+    <row r="33" spans="10:22">
+      <c r="J33" s="26"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="6"/>
+    </row>
+    <row r="34" spans="10:22">
+      <c r="J34" s="26"/>
+      <c r="K34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="6"/>
+    </row>
+    <row r="35" spans="10:22">
+      <c r="J35" s="26"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="6"/>
+    </row>
+    <row r="36" spans="10:22">
+      <c r="J36" s="26"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="6"/>
+    </row>
+    <row r="37" spans="10:22">
+      <c r="J37" s="26"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="6"/>
+    </row>
+    <row r="38" spans="10:22">
+      <c r="J38" s="26"/>
+      <c r="K38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="6"/>
+    </row>
+    <row r="39" spans="10:22">
+      <c r="J39" s="4"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="6"/>
+    </row>
+    <row r="40" spans="10:22">
+      <c r="J40" s="8"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="9"/>
+    </row>
+    <row r="41" spans="10:22">
+      <c r="J41" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="5"/>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="K25" t="s">
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="3"/>
+    </row>
+    <row r="42" spans="10:22">
+      <c r="J42" s="26"/>
+      <c r="K42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="6"/>
+    </row>
+    <row r="43" spans="10:22">
+      <c r="J43" s="26"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="6"/>
+    </row>
+    <row r="44" spans="10:22">
+      <c r="J44" s="26"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="6"/>
+    </row>
+    <row r="45" spans="10:22">
+      <c r="J45" s="26"/>
+      <c r="K45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="6"/>
+    </row>
+    <row r="46" spans="10:22">
+      <c r="J46" s="26"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="6"/>
+    </row>
+    <row r="47" spans="10:22">
+      <c r="J47" s="26"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="6"/>
+    </row>
+    <row r="48" spans="10:22">
+      <c r="J48" s="26"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="6"/>
+    </row>
+    <row r="49" spans="10:22">
+      <c r="J49" s="26"/>
+      <c r="K49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="6"/>
+    </row>
+    <row r="50" spans="10:22">
+      <c r="J50" s="30"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+      <c r="T50" s="11"/>
+      <c r="U50" s="11"/>
+      <c r="V50" s="9"/>
+    </row>
+    <row r="51" spans="10:22">
+      <c r="J51" s="12"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="14"/>
+    </row>
+    <row r="52" spans="10:22">
+      <c r="J52" s="15"/>
+      <c r="K52" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="17"/>
+    </row>
+    <row r="53" spans="10:22">
+      <c r="J53" s="18"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="14"/>
+      <c r="P53" s="19"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13"/>
+      <c r="S53" s="19"/>
+      <c r="T53" s="13"/>
+      <c r="U53" s="13"/>
+      <c r="V53" s="14"/>
+    </row>
+    <row r="54" spans="10:22">
+      <c r="J54" s="18"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="21"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="23"/>
+      <c r="S54" s="22"/>
+      <c r="T54" s="20"/>
+      <c r="U54" s="23"/>
+      <c r="V54" s="14"/>
+    </row>
+    <row r="55" spans="10:22">
+      <c r="J55" s="18"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="13"/>
+      <c r="U55" s="13"/>
+      <c r="V55" s="14"/>
+    </row>
+    <row r="56" spans="10:22">
+      <c r="J56" s="18"/>
+      <c r="K56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N25" s="7"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="1"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="M26" s="5"/>
-      <c r="N26" s="11"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="11"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="11"/>
-    </row>
-    <row r="29" spans="1:22">
-      <c r="J29" s="13" t="s">
-        <v>8</v>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="15"/>
+      <c r="R56" s="16"/>
+      <c r="S56" s="18"/>
+      <c r="T56" s="15"/>
+      <c r="U56" s="16"/>
+      <c r="V56" s="14"/>
+    </row>
+    <row r="57" spans="10:22">
+      <c r="J57" s="18"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="23"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="18"/>
+      <c r="R57" s="13"/>
+      <c r="S57" s="20"/>
+      <c r="T57" s="18"/>
+      <c r="U57" s="13"/>
+      <c r="V57" s="14"/>
+    </row>
+    <row r="58" spans="10:22">
+      <c r="J58" s="18"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+      <c r="P58" s="13"/>
+      <c r="Q58" s="13"/>
+      <c r="R58" s="13"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="13"/>
+      <c r="U58" s="13"/>
+      <c r="V58" s="14"/>
+    </row>
+    <row r="59" spans="10:22">
+      <c r="J59" s="20"/>
+      <c r="K59" s="23"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="23"/>
+      <c r="N59" s="23"/>
+      <c r="O59" s="23"/>
+      <c r="P59" s="23"/>
+      <c r="Q59" s="23"/>
+      <c r="R59" s="23"/>
+      <c r="S59" s="23"/>
+      <c r="T59" s="23"/>
+      <c r="U59" s="23"/>
+      <c r="V59" s="21"/>
+    </row>
+    <row r="60" spans="10:22">
+      <c r="J60" s="27" t="s">
+        <v>9</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="16"/>
+      <c r="V60" s="17"/>
+    </row>
+    <row r="61" spans="10:22">
+      <c r="J61" s="28"/>
+      <c r="K61" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="2"/>
-    </row>
-    <row r="30" spans="1:22">
-      <c r="J30" s="14"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="3"/>
-    </row>
-    <row r="31" spans="1:22">
-      <c r="J31" s="14"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-      <c r="U31" s="10"/>
-      <c r="V31" s="3"/>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="J32" s="14"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
-      <c r="U32" s="10"/>
-      <c r="V32" s="3"/>
-    </row>
-    <row r="33" spans="10:22">
-      <c r="J33" s="14"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
-      <c r="V33" s="3"/>
-    </row>
-    <row r="34" spans="10:22">
-      <c r="J34" s="14"/>
-      <c r="K34" s="10" t="s">
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="13"/>
+      <c r="Q61" s="13"/>
+      <c r="R61" s="13"/>
+      <c r="S61" s="13"/>
+      <c r="T61" s="13"/>
+      <c r="U61" s="13"/>
+      <c r="V61" s="14"/>
+    </row>
+    <row r="62" spans="10:22">
+      <c r="J62" s="28"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="13"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="13"/>
+      <c r="U62" s="13"/>
+      <c r="V62" s="14"/>
+    </row>
+    <row r="63" spans="10:22">
+      <c r="J63" s="28"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+      <c r="P63" s="13"/>
+      <c r="Q63" s="13"/>
+      <c r="R63" s="13"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="13"/>
+      <c r="U63" s="13"/>
+      <c r="V63" s="14"/>
+    </row>
+    <row r="64" spans="10:22">
+      <c r="J64" s="28"/>
+      <c r="K64" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="3"/>
-    </row>
-    <row r="35" spans="10:22">
-      <c r="J35" s="14"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10"/>
-      <c r="V35" s="3"/>
-    </row>
-    <row r="36" spans="10:22">
-      <c r="J36" s="14"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="3"/>
-    </row>
-    <row r="37" spans="10:22">
-      <c r="J37" s="14"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
-      <c r="V37" s="3"/>
-    </row>
-    <row r="38" spans="10:22">
-      <c r="J38" s="14"/>
-      <c r="K38" s="10" t="s">
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+      <c r="P64" s="13"/>
+      <c r="Q64" s="13"/>
+      <c r="R64" s="13"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="13"/>
+      <c r="U64" s="13"/>
+      <c r="V64" s="14"/>
+    </row>
+    <row r="65" spans="10:22">
+      <c r="J65" s="28"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13"/>
+      <c r="P65" s="13"/>
+      <c r="Q65" s="13"/>
+      <c r="R65" s="13"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="13"/>
+      <c r="U65" s="13"/>
+      <c r="V65" s="14"/>
+    </row>
+    <row r="66" spans="10:22">
+      <c r="J66" s="28"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+      <c r="P66" s="13"/>
+      <c r="Q66" s="13"/>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="13"/>
+      <c r="U66" s="13"/>
+      <c r="V66" s="14"/>
+    </row>
+    <row r="67" spans="10:22">
+      <c r="J67" s="28"/>
+      <c r="K67" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
-      <c r="U38" s="10"/>
-      <c r="V38" s="3"/>
-    </row>
-    <row r="39" spans="10:22">
-      <c r="J39" s="11"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
-      <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="10:22">
-      <c r="J40" s="4"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-      <c r="V40" s="6"/>
-    </row>
-    <row r="41" spans="10:22">
-      <c r="J41" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="10:22">
-      <c r="J42" s="12"/>
-    </row>
-    <row r="43" spans="10:22">
-      <c r="J43" s="12"/>
-    </row>
-    <row r="44" spans="10:22">
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45" spans="10:22">
-      <c r="J45" s="12"/>
-    </row>
-    <row r="46" spans="10:22">
-      <c r="J46" s="12"/>
-    </row>
-    <row r="47" spans="10:22">
-      <c r="J47" s="12"/>
-    </row>
-    <row r="48" spans="10:22">
-      <c r="J48" s="12"/>
-    </row>
-    <row r="49" spans="10:10">
-      <c r="J49" s="12"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13"/>
+      <c r="P67" s="13"/>
+      <c r="Q67" s="13"/>
+      <c r="R67" s="13"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="13"/>
+      <c r="U67" s="13"/>
+      <c r="V67" s="14"/>
+    </row>
+    <row r="68" spans="10:22">
+      <c r="J68" s="29"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="23"/>
+      <c r="P68" s="23"/>
+      <c r="Q68" s="23"/>
+      <c r="R68" s="23"/>
+      <c r="S68" s="23"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="23"/>
+      <c r="V68" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="J29:J38"/>
-    <mergeCell ref="J41:J49"/>
+    <mergeCell ref="J60:J68"/>
+    <mergeCell ref="J41:J50"/>
+    <mergeCell ref="B25:H30"/>
+    <mergeCell ref="A25:A30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Document/Buck/Buck.xlsx
+++ b/Document/Buck/Buck.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE0C1CF-5C92-42E6-A371-9E9CC6AD5ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C26767-5275-4D48-A96A-89C44177297E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Reference matlab" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Q1导通Q2关断给L1充电电感电流缓慢上升电感两端电压VL=VIN-VOUT</t>
   </si>
@@ -80,12 +80,18 @@
 如果不做零电流检测 ZCS，永远不会进入 DCM，只会进入CCM 负电流模式。这就是为什么我们调试逆变器的时候放电情况下，逆变器空载的时候电压还是稳定。 
 ✅ 同步 Buck 想要 DCM：必须增加下管的 ZCS 检测，电感电流到 0 立刻关断下管，防止电流倒灌。</t>
   </si>
+  <si>
+    <t>Simulink仿真----降压(Buck)变换器_simulink里面的diode的m-CSDN博客</t>
+  </si>
+  <si>
+    <t>(6 条消息) 纯小白入门！基于MATLAB的simlink的同步BUCK电源仿真及通过system identification的闭环PID自动调参 - 知乎</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +103,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -235,12 +249,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -343,8 +360,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4315,9 +4336,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" display="https://blog.csdn.net/qq_42078934/article/details/127007036" xr:uid="{44944EA5-C680-43E7-8C3F-949C5B91A85E}"/>
+    <hyperlink ref="A2" r:id="rId2" display="https://zhuanlan.zhihu.com/p/623929542" xr:uid="{FBF388BB-7B64-409E-87CB-7CF125D20BCB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
